--- a/agriculture 37.xlsx
+++ b/agriculture 37.xlsx
@@ -241,13 +241,13 @@
     <t xml:space="preserve">2018-19</t>
   </si>
   <si>
+    <t xml:space="preserve">Unit:- </t>
+  </si>
+  <si>
     <t xml:space="preserve">Source:Economic and Political Weekly Research Foundation (1950-2019)</t>
   </si>
   <si>
-    <t xml:space="preserve">Source Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1962-63 to 2013-14: Plantation Crops: Tea:-&gt; Tea Board India</t>
+    <t xml:space="preserve">Source Description:- 1962-63 to 2013-14: Plantation Crops: Tea:-&gt; Tea Board India</t>
   </si>
   <si>
     <t xml:space="preserve">Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
@@ -261,7 +261,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -298,6 +298,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -349,7 +354,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -374,6 +379,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -391,8 +400,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AG1048576"/>
-  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AG61"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11.48"/>
@@ -2581,28 +2590,97 @@
       <c r="O57" s="3"/>
       <c r="P57" s="3"/>
     </row>
-    <row r="58" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="59" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="3"/>
+      <c r="J58" s="3"/>
+      <c r="K58" s="3"/>
+      <c r="L58" s="3"/>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
+      <c r="O58" s="3"/>
+      <c r="P58" s="3"/>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="6" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="60" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
+      <c r="M59" s="6"/>
+      <c r="N59" s="6"/>
+      <c r="O59" s="6"/>
+      <c r="P59" s="6"/>
+      <c r="Q59" s="6"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="6" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="61" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="6"/>
+      <c r="N60" s="6"/>
+      <c r="O60" s="6"/>
+      <c r="P60" s="6"/>
+      <c r="Q60" s="6"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="6" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="6"/>
+      <c r="N61" s="6"/>
+      <c r="O61" s="6"/>
+      <c r="P61" s="6"/>
+      <c r="Q61" s="6"/>
+    </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A58:Q58"/>
+    <mergeCell ref="A59:Q59"/>
+    <mergeCell ref="A60:Q60"/>
+    <mergeCell ref="A61:Q61"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/agriculture 37.xlsx
+++ b/agriculture 37.xlsx
@@ -241,7 +241,7 @@
     <t xml:space="preserve">2018-19</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- </t>
+    <t xml:space="preserve">Unit:- Percentage(%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source:Economic and Political Weekly Research Foundation (1950-2019)</t>
@@ -261,7 +261,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -298,11 +298,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -379,7 +374,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -401,7 +396,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AG61"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11.48"/>

--- a/agriculture 37.xlsx
+++ b/agriculture 37.xlsx
@@ -241,7 +241,7 @@
     <t xml:space="preserve">2018-19</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- Percentage(%)</t>
+    <t xml:space="preserve">Unit:- Percentage (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source:Economic and Political Weekly Research Foundation (1950-2019)</t>
@@ -396,7 +396,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AG61"/>
-  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.82421875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11.48"/>
